--- a/sheets/국악이꽃피는나무/검수/상사화.xlsx
+++ b/sheets/국악이꽃피는나무/검수/상사화.xlsx
@@ -14539,28 +14539,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="86.26" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="86.26" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="86.26" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="86.26" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="86.26" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="86.26" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="86.26" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="86.26" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="86.26" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="86.26" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="86.26" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="86.26" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="57.97" customHeight="true">
+    <row r="16" ht="64.52" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="86.26" customHeight="true">
+    <row r="17" ht="96.05" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="86.26" customHeight="true">
+    <row r="18" ht="96.05" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
       <c r="P18" s="21"/>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="86.26" customHeight="true">
+    <row r="19" ht="96.05" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="86.26" customHeight="true">
+    <row r="20" ht="96.05" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="86.26" customHeight="true">
+    <row r="21" ht="96.05" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="86.26" customHeight="true">
+    <row r="22" ht="96.05" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
       <c r="P22" s="21"/>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="86.26" customHeight="true">
+    <row r="23" ht="96.05" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
       <c r="P23" s="21"/>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="86.26" customHeight="true">
+    <row r="24" ht="96.05" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
       <c r="P24" s="21"/>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="86.26" customHeight="true">
+    <row r="25" ht="96.05" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
       <c r="P25" s="21"/>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="86.26" customHeight="true">
+    <row r="26" ht="96.05" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="86.26" customHeight="true">
+    <row r="27" ht="96.05" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="86.26" customHeight="true">
+    <row r="28" ht="96.05" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
     <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="57.97" customHeight="true">
+    <row r="30" ht="64.52" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
     </row>
-    <row r="31" ht="86.26" customHeight="true">
+    <row r="31" ht="96.05" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="Q31" s="22"/>
     </row>
-    <row r="32" ht="86.26" customHeight="true">
+    <row r="32" ht="96.05" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="86.26" customHeight="true">
+    <row r="33" ht="96.05" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="86.26" customHeight="true">
+    <row r="34" ht="96.05" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="86.26" customHeight="true">
+    <row r="35" ht="96.05" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="86.26" customHeight="true">
+    <row r="36" ht="96.05" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
       </c>
       <c r="Q36" s="24"/>
     </row>
-    <row r="37" ht="86.26" customHeight="true">
+    <row r="37" ht="96.05" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="86.26" customHeight="true">
+    <row r="38" ht="96.05" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="Q38" s="23"/>
     </row>
-    <row r="39" ht="86.26" customHeight="true">
+    <row r="39" ht="96.05" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="Q39" s="24"/>
     </row>
-    <row r="40" ht="86.26" customHeight="true">
+    <row r="40" ht="96.05" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="Q40" s="22"/>
     </row>
-    <row r="41" ht="86.26" customHeight="true">
+    <row r="41" ht="96.05" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="Q41" s="23"/>
     </row>
-    <row r="42" ht="86.26" customHeight="true">
+    <row r="42" ht="96.05" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
     <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="57.97" customHeight="true">
+    <row r="44" ht="64.52" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
       <c r="P44" s="20"/>
       <c r="Q44" s="20"/>
     </row>
-    <row r="45" ht="86.26" customHeight="true">
+    <row r="45" ht="96.05" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
       <c r="P45" s="21"/>
       <c r="Q45" s="22"/>
     </row>
-    <row r="46" ht="86.26" customHeight="true">
+    <row r="46" ht="96.05" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
       <c r="P46" s="21"/>
       <c r="Q46" s="23"/>
     </row>
-    <row r="47" ht="86.26" customHeight="true">
+    <row r="47" ht="96.05" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
       <c r="P47" s="21"/>
       <c r="Q47" s="24"/>
     </row>
-    <row r="48" ht="86.26" customHeight="true">
+    <row r="48" ht="96.05" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       <c r="P48" s="21"/>
       <c r="Q48" s="22"/>
     </row>
-    <row r="49" ht="86.26" customHeight="true">
+    <row r="49" ht="96.05" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
       <c r="P49" s="21"/>
       <c r="Q49" s="23"/>
     </row>
-    <row r="50" ht="86.26" customHeight="true">
+    <row r="50" ht="96.05" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
       <c r="P50" s="21"/>
       <c r="Q50" s="24"/>
     </row>
-    <row r="51" ht="86.26" customHeight="true">
+    <row r="51" ht="96.05" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
       <c r="P51" s="21"/>
       <c r="Q51" s="22"/>
     </row>
-    <row r="52" ht="86.26" customHeight="true">
+    <row r="52" ht="96.05" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
       <c r="P52" s="21"/>
       <c r="Q52" s="23"/>
     </row>
-    <row r="53" ht="86.26" customHeight="true">
+    <row r="53" ht="96.05" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
       <c r="P53" s="21"/>
       <c r="Q53" s="24"/>
     </row>
-    <row r="54" ht="86.26" customHeight="true">
+    <row r="54" ht="96.05" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="86.26" customHeight="true">
+    <row r="55" ht="96.05" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="86.26" customHeight="true">
+    <row r="56" ht="96.05" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
     <row r="57" ht="6.0" customHeight="true">
       <c r="A57" s="0"/>
     </row>
-    <row r="58" ht="57.97" customHeight="true">
+    <row r="58" ht="64.52" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="20" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
       <c r="P58" s="20"/>
       <c r="Q58" s="20"/>
     </row>
-    <row r="59" ht="86.26" customHeight="true">
+    <row r="59" ht="96.05" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21"/>
       <c r="C59" s="22"/>
@@ -18070,7 +18070,7 @@
       <c r="P59" s="21"/>
       <c r="Q59" s="22"/>
     </row>
-    <row r="60" ht="86.26" customHeight="true">
+    <row r="60" ht="96.05" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21"/>
       <c r="C60" s="23"/>
@@ -18097,7 +18097,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="86.26" customHeight="true">
+    <row r="61" ht="96.05" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21"/>
       <c r="C61" s="24"/>
@@ -18124,7 +18124,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="86.26" customHeight="true">
+    <row r="62" ht="96.05" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21"/>
       <c r="C62" s="22"/>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="86.26" customHeight="true">
+    <row r="63" ht="96.05" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21"/>
       <c r="C63" s="23"/>
@@ -18178,7 +18178,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="86.26" customHeight="true">
+    <row r="64" ht="96.05" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21"/>
       <c r="C64" s="24"/>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="Q64" s="24"/>
     </row>
-    <row r="65" ht="86.26" customHeight="true">
+    <row r="65" ht="96.05" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21"/>
       <c r="C65" s="22"/>
@@ -18228,7 +18228,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="86.26" customHeight="true">
+    <row r="66" ht="96.05" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21"/>
       <c r="C66" s="23"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="Q66" s="23"/>
     </row>
-    <row r="67" ht="86.26" customHeight="true">
+    <row r="67" ht="96.05" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21"/>
       <c r="C67" s="24"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="Q67" s="24"/>
     </row>
-    <row r="68" ht="86.26" customHeight="true">
+    <row r="68" ht="96.05" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21"/>
       <c r="C68" s="22"/>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="Q68" s="22"/>
     </row>
-    <row r="69" ht="86.26" customHeight="true">
+    <row r="69" ht="96.05" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21"/>
       <c r="C69" s="23"/>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="Q69" s="23"/>
     </row>
-    <row r="70" ht="86.26" customHeight="true">
+    <row r="70" ht="96.05" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21"/>
       <c r="C70" s="24"/>
@@ -18353,7 +18353,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <rowBreaks count="4" manualBreakCount="4">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
